--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A32890-48E2-4FB0-8D60-A78EF2D9AEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB6D000-D79D-4405-AFC4-57B1CF095C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="181">
   <si>
     <t>版本</t>
   </si>
@@ -3596,6 +3596,14 @@
   </si>
   <si>
     <t>启用Karatsuba卷积优化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H41.pas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合Laurent核构造并缩小Karatsuba叶节点</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4065,7 +4073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="2" bestFit="1" customWidth="1"/>
@@ -5326,9 +5334,27 @@
         <v>178</v>
       </c>
     </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB6D000-D79D-4405-AFC4-57B1CF095C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658A574C-1969-4135-919B-929D33E74B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="183">
   <si>
     <t>版本</t>
   </si>
@@ -3604,6 +3604,14 @@
   </si>
   <si>
     <t>融合Laurent核构造并缩小Karatsuba叶节点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H42.pas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用反射对称性将一次全长卷积改为两次半长卷积</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4073,7 +4081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="2" bestFit="1" customWidth="1"/>
@@ -5349,6 +5357,23 @@
       </c>
       <c r="E74" s="11" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658A574C-1969-4135-919B-929D33E74B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB22CC2-5EE7-4B76-9C96-CE53D13484D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,19 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="183">
-  <si>
-    <t>版本</t>
-  </si>
-  <si>
-    <t>计算原理</t>
-  </si>
-  <si>
-    <t>时间复杂度</t>
-  </si>
-  <si>
-    <t>空间复杂度</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="180">
   <si>
     <t>O(n²)</t>
   </si>
@@ -89,7 +76,7 @@
   </si>
   <si>
     <t>O(n³)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10.pas</t>
@@ -129,7 +116,7 @@
   </si>
   <si>
     <t>O(n)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H2.pas</t>
@@ -234,9 +221,6 @@
     <t>diandeng10_a_faster2_png_H35.pas</t>
   </si>
   <si>
-    <t>和前面主线的关系</t>
-  </si>
-  <si>
     <t>diandeng11_test.pas</t>
   </si>
   <si>
@@ -285,7 +269,7 @@
       </rPr>
       <t>时间</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -299,7 +283,7 @@
       </rPr>
       <t>空间</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -313,7 +297,7 @@
       </rPr>
       <t>版本区别</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -401,7 +385,7 @@
       </rPr>
       <t>带状高斯消元</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -464,7 +448,7 @@
       </rPr>
       <t>多项式求逆法</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -477,7 +461,7 @@
       </rPr>
       <t>多项式求逆法</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -490,7 +474,7 @@
       </rPr>
       <t>多项式求逆法</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -526,7 +510,7 @@
       </rPr>
       <t>5</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -548,7 +532,7 @@
       </rPr>
       <t>n</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -572,7 +556,7 @@
       </rPr>
       <t>6</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -633,7 +617,7 @@
       </rPr>
       <t>高斯消元</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -679,7 +663,7 @@
       </rPr>
       <t>png</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -692,7 +676,7 @@
       </rPr>
       <t>斜点亮规则</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -760,7 +744,7 @@
       </rPr>
       <t>提取为函数</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -774,7 +758,7 @@
       </rPr>
       <t>首行方程</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -787,7 +771,7 @@
       </rPr>
       <t>反色</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -809,7 +793,7 @@
       </rPr>
       <t>TMAT</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -850,7 +834,7 @@
       </rPr>
       <t>MakeMat</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -863,7 +847,7 @@
       </rPr>
       <t>统一下标</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -913,7 +897,7 @@
       </rPr>
       <t>优化</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -973,7 +957,7 @@
       </rPr>
       <t>n^2</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -986,7 +970,7 @@
       </rPr>
       <t>周期边界版，上下左右都做环绕，等价于环面版点灯</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -999,7 +983,7 @@
       </rPr>
       <t>首行方程法</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1031,7 +1015,7 @@
       </rPr>
       <t>保存所有递推层</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1091,7 +1075,7 @@
       </rPr>
       <t xml:space="preserve"> lk[j,:,k]</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1142,7 +1126,7 @@
       </rPr>
       <t>快进递推</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1174,7 +1158,7 @@
       </rPr>
       <t>的中间递推矩阵，不真正求解</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1244,7 +1228,7 @@
       </rPr>
       <t>全局点灯矩阵</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1295,7 +1279,7 @@
       </rPr>
       <t>块更新</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1901,7 +1885,7 @@
       </rPr>
       <t>合并重写，整体从矩阵法进一步转向多项式法</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3464,15 +3448,15 @@
   </si>
   <si>
     <t>diandeng1.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H36.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3504,7 +3488,7 @@
       </rPr>
       <t>实验</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3517,7 +3501,7 @@
       </rPr>
       <t>十字递推图案生成</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3533,7 +3517,7 @@
       </rPr>
       <t>图片版</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3555,11 +3539,11 @@
       </rPr>
       <t>makemat</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H37.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3572,68 +3556,67 @@
       </rPr>
       <t>优化位运算版调用和边界位访问开销</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H38.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>优化位运算版调用和边界位访问开销</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>优化z，减少反复执行多项式</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H39.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H40.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>启用Karatsuba卷积优化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H41.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>融合Laurent核构造并缩小Karatsuba叶节点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H42.pas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>利用反射对称性将一次全长卷积改为两次半长卷积</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H43.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合 y/y_ 耦合递推并通过双缓冲轮换消除重复计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3730,41 +3713,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4081,1338 +4061,1321 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="36.375" style="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E64" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1AA9F0-B573-4686-8F6B-FFCB6A265BB9}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="40.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="36.375" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="B23" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>179</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB22CC2-5EE7-4B76-9C96-CE53D13484D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD37B0B8-0510-43A1-AFD9-6355DCB082AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="182">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3604,6 +3604,14 @@
   </si>
   <si>
     <t>融合 y/y_ 耦合递推并通过双缓冲轮换消除重复计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将两次Karatsuba卷积融合为一次，复用分裂与异或</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H44.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4061,7 +4069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5373,6 +5381,23 @@
         <v>179</v>
       </c>
     </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD37B0B8-0510-43A1-AFD9-6355DCB082AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D7FFD1-A28B-4757-923E-60CA09DA0D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="10425" yWindow="2775" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="184">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3612,6 +3612,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H44.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Karatsuba按有效长度跳过补零分支，避免无效高位递归卷积</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H45.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4069,7 +4077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5398,6 +5406,23 @@
         <v>180</v>
       </c>
     </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D7FFD1-A28B-4757-923E-60CA09DA0D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B542D1-9498-4EC5-9B1D-74B0545D6563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10425" yWindow="2775" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="186">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3620,6 +3620,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H45.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H46.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将二次幂补零Karatsuba改为按实际32位块数进行非等长递归</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4077,7 +4085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5423,6 +5431,23 @@
         <v>182</v>
       </c>
     </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>185</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B542D1-9498-4EC5-9B1D-74B0545D6563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139DE3FB-C981-4F96-A1DA-8E0B2B3D5A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="188">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3628,6 +3628,14 @@
   </si>
   <si>
     <t>将二次幂补零Karatsuba改为按实际32位块数进行非等长递归</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用一个Bézout系数Karatsuba乘法与32系数分块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H47.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4085,7 +4093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5448,6 +5456,23 @@
         <v>185</v>
       </c>
     </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139DE3FB-C981-4F96-A1DA-8E0B2B3D5A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A481DB9-6060-491B-A38A-8B49F8E70881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="190">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3636,6 +3636,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H47.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用Laurent核递归消除零填充，Karatsuba叶节点统一256位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H48.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4093,7 +4101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5473,6 +5481,23 @@
         <v>186</v>
       </c>
     </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/diandeng版本说明.xlsx
+++ b/diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A481DB9-6060-491B-A38A-8B49F8E70881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57183E51-1B0B-4871-82B8-41901300CB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="192">
   <si>
     <t>O(n²)</t>
   </si>
@@ -3644,6 +3644,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H48.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将z阶段的两个相同Karatsuba卷积合并为一次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H49.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4101,7 +4109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -5498,6 +5506,23 @@
         <v>188</v>
       </c>
     </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
